--- a/OUTPUT/direct_Q9KNW6_Vibrio_cholerae_O1_biovar_El_Tor_str__N16961.xlsx
+++ b/OUTPUT/direct_Q9KNW6_Vibrio_cholerae_O1_biovar_El_Tor_str__N16961.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7363054778088765</v>
       </c>
     </row>
   </sheetData>
